--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_23-03-2026.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_23-03-2026.xlsx
@@ -1,15 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Priyanka\Documents\Price_Comp_Dashboard\Compititor's_Price\Celotex_Prices\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{674A1150-233B-4913-8A3A-ABDC00359EEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -1075,12 +1081,6 @@
     <t>£44.93</t>
   </si>
   <si>
-    <t>£9105.12</t>
-  </si>
-  <si>
-    <t>Error: could not convert string to float: '1,037.11'</t>
-  </si>
-  <si>
     <t>£32.58</t>
   </si>
   <si>
@@ -1175,13 +1175,19 @@
   </si>
   <si>
     <t>£1517.76</t>
+  </si>
+  <si>
+    <t>£758.76</t>
+  </si>
+  <si>
+    <t>£1037.11</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1244,13 +1250,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1288,7 +1302,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -1322,6 +1336,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -1356,9 +1371,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1531,11 +1547,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:R29"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:18">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1591,7 +1607,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:18">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>18</v>
       </c>
@@ -1644,10 +1660,10 @@
         <v>338</v>
       </c>
       <c r="R2" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
-    <row r="3" spans="1:18">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>19</v>
       </c>
@@ -1703,7 +1719,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="4" spans="1:18">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>20</v>
       </c>
@@ -1756,10 +1772,10 @@
         <v>340</v>
       </c>
       <c r="R4" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
-    <row r="5" spans="1:18">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>21</v>
       </c>
@@ -1812,10 +1828,10 @@
         <v>341</v>
       </c>
       <c r="R5" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
-    <row r="6" spans="1:18">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>22</v>
       </c>
@@ -1868,10 +1884,10 @@
         <v>342</v>
       </c>
       <c r="R6" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
-    <row r="7" spans="1:18">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>23</v>
       </c>
@@ -1924,10 +1940,10 @@
         <v>343</v>
       </c>
       <c r="R7" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
-    <row r="8" spans="1:18">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>24</v>
       </c>
@@ -1980,10 +1996,10 @@
         <v>344</v>
       </c>
       <c r="R8" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
-    <row r="9" spans="1:18">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>25</v>
       </c>
@@ -2036,10 +2052,10 @@
         <v>345</v>
       </c>
       <c r="R9" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
     </row>
-    <row r="10" spans="1:18">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>26</v>
       </c>
@@ -2092,10 +2108,10 @@
         <v>346</v>
       </c>
       <c r="R10" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
-    <row r="11" spans="1:18">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>27</v>
       </c>
@@ -2148,10 +2164,10 @@
         <v>347</v>
       </c>
       <c r="R11" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
-    <row r="12" spans="1:18">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>28</v>
       </c>
@@ -2204,10 +2220,10 @@
         <v>348</v>
       </c>
       <c r="R12" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
     </row>
-    <row r="13" spans="1:18">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>29</v>
       </c>
@@ -2260,10 +2276,10 @@
         <v>349</v>
       </c>
       <c r="R13" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
     </row>
-    <row r="14" spans="1:18">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>30</v>
       </c>
@@ -2316,10 +2332,10 @@
         <v>350</v>
       </c>
       <c r="R14" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
     </row>
-    <row r="15" spans="1:18">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>31</v>
       </c>
@@ -2375,7 +2391,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="16" spans="1:18">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>32</v>
       </c>
@@ -2428,10 +2444,10 @@
         <v>352</v>
       </c>
       <c r="R16" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
     </row>
-    <row r="17" spans="1:18">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>33</v>
       </c>
@@ -2481,13 +2497,13 @@
         <v>326</v>
       </c>
       <c r="Q17" t="s">
-        <v>353</v>
+        <v>385</v>
       </c>
       <c r="R17" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="18" spans="1:18">
+    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>34</v>
       </c>
@@ -2537,13 +2553,13 @@
         <v>327</v>
       </c>
       <c r="Q18" t="s">
-        <v>354</v>
+        <v>386</v>
       </c>
       <c r="R18" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
     </row>
-    <row r="19" spans="1:18">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>35</v>
       </c>
@@ -2593,13 +2609,13 @@
         <v>328</v>
       </c>
       <c r="Q19" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="R19" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
-    <row r="20" spans="1:18">
+    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>36</v>
       </c>
@@ -2649,13 +2665,13 @@
         <v>329</v>
       </c>
       <c r="Q20" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="R20" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
-    <row r="21" spans="1:18">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>37</v>
       </c>
@@ -2708,10 +2724,10 @@
         <v>278</v>
       </c>
       <c r="R21" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
     </row>
-    <row r="22" spans="1:18">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>38</v>
       </c>
@@ -2761,13 +2777,13 @@
         <v>331</v>
       </c>
       <c r="Q22" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="R22" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
-    <row r="23" spans="1:18">
+    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>39</v>
       </c>
@@ -2817,13 +2833,13 @@
         <v>332</v>
       </c>
       <c r="Q23" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="R23" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
     </row>
-    <row r="24" spans="1:18">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>40</v>
       </c>
@@ -2873,13 +2889,13 @@
         <v>333</v>
       </c>
       <c r="Q24" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="R24" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
-    <row r="25" spans="1:18">
+    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>41</v>
       </c>
@@ -2935,7 +2951,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="26" spans="1:18">
+    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>42</v>
       </c>
@@ -2985,13 +3001,13 @@
         <v>334</v>
       </c>
       <c r="Q26" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="R26" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
     </row>
-    <row r="27" spans="1:18">
+    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>43</v>
       </c>
@@ -3041,13 +3057,13 @@
         <v>335</v>
       </c>
       <c r="Q27" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="R27" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
     </row>
-    <row r="28" spans="1:18">
+    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>44</v>
       </c>
@@ -3097,13 +3113,13 @@
         <v>336</v>
       </c>
       <c r="Q28" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="R28" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
     </row>
-    <row r="29" spans="1:18">
+    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>45</v>
       </c>
@@ -3156,7 +3172,7 @@
         <v>101</v>
       </c>
       <c r="R29" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
   </sheetData>
